--- a/redmine-logger/git_commits_excel.xlsx
+++ b/redmine-logger/git_commits_excel.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-04-20</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B2" t="str">
         <v>Daily Scrum Call</v>
@@ -447,283 +447,30 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04-20</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B3" t="str">
-        <v>commit fetch api inprocess</v>
+        <v>feat: add APU Redmine upload endpoint, improve commit merging logic with merge-commit comparison, and update project configuration.</v>
       </c>
       <c r="C3" t="str">
-        <v>Implement Fetch API for Logging</v>
+        <v>feat: add APU Redmine upload endpoint, improve commit merging logic with merge-commit comparison, and update project configuration.</v>
       </c>
       <c r="D3" t="str">
-        <v>Feature</v>
+        <v>Development &amp; Configuration</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3" t="str">
-        <v>daf6463f1004e2725a82357bd4957c35630d104d</v>
+        <v>ec35813a7537f2b431bd43f8057dd00b05a205e8</v>
       </c>
       <c r="G3" t="str">
-        <v>main</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Daily Scrum Call</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Daily Scrum Call</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Meeting</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="G4" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Merge remote-tracking branch 'origin/mvp-2'</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Integrate MVP-2 Branch</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Integration/Merge</v>
-      </c>
-      <c r="E5">
-        <v>0.62</v>
-      </c>
-      <c r="F5" t="str">
-        <v>2c196382af12760824f6b7e8ae5274b373f3893c</v>
-      </c>
-      <c r="G5" t="str">
-        <v>main</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B6" t="str">
-        <v>mvp-2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Enhance User-Specific Excel Handling</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Refactor</v>
-      </c>
-      <c r="E6">
-        <v>0.62</v>
-      </c>
-      <c r="F6" t="str">
-        <v>9921664a3ae378336925a77461fc71730f17cfb7</v>
-      </c>
-      <c r="G6" t="str">
-        <v>main</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B7" t="str">
-        <v>redmine connection feature added</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Add Redmine Connection Feature</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Feature</v>
-      </c>
-      <c r="E7">
-        <v>1.23</v>
-      </c>
-      <c r="F7" t="str">
-        <v>7b82d9f3adbdd1f8080c38821805c2666647565f</v>
-      </c>
-      <c r="G7" t="str">
-        <v>main</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B8" t="str">
-        <v>prod ready</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Prepare Application for Production</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Integration/Merge</v>
-      </c>
-      <c r="E8">
-        <v>0.62</v>
-      </c>
-      <c r="F8" t="str">
-        <v>cabab140d34af0492c9f1a3521ae286fcf4e6a1d</v>
-      </c>
-      <c r="G8" t="str">
-        <v>main</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B9" t="str">
-        <v>deployment setup</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Deployment Setup and API Enhancements</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Integration/Merge</v>
-      </c>
-      <c r="E9">
-        <v>0.92</v>
-      </c>
-      <c r="F9" t="str">
-        <v>1f619869b38ffd400abae6d7d1eb61163946728a</v>
-      </c>
-      <c r="G9" t="str">
-        <v>main</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B10" t="str">
-        <v>MVP-1</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Enhance Commit Fetching Logic</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Feature</v>
-      </c>
-      <c r="E10">
-        <v>0.62</v>
-      </c>
-      <c r="F10" t="str">
-        <v>9e26a2e2d3d2633de8816a12e501299931a3485b</v>
-      </c>
-      <c r="G10" t="str">
-        <v>main</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B11" t="str">
-        <v>working fine</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Enhance Commit Fetching Logic</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Feature</v>
-      </c>
-      <c r="E11">
-        <v>0.62</v>
-      </c>
-      <c r="F11" t="str">
-        <v>c06603001ddd34dda0667adcf9e968290a45863e</v>
-      </c>
-      <c r="G11" t="str">
-        <v>main</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B12" t="str">
-        <v>ui fix</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Add UI Correction Script</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Feature</v>
-      </c>
-      <c r="E12">
-        <v>0.62</v>
-      </c>
-      <c r="F12" t="str">
-        <v>02e12417a80bff020e0cdae272c5185255fcd3bc</v>
-      </c>
-      <c r="G12" t="str">
-        <v>main</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B13" t="str">
-        <v>apu sheet creation</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Creation of APU Tracking Sheet</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Feature</v>
-      </c>
-      <c r="E13">
-        <v>1.23</v>
-      </c>
-      <c r="F13" t="str">
-        <v>856676533897f232eb2c0153b6d570adef0a7310</v>
-      </c>
-      <c r="G13" t="str">
-        <v>main</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B14" t="str">
-        <v>commit fetch done</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Enhance Commit Fetch Functionality</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Refactor</v>
-      </c>
-      <c r="E14">
-        <v>0.9</v>
-      </c>
-      <c r="F14" t="str">
-        <v>d6a26a233e1d1c46a4bbc6e2b34c4fb168a14a9c</v>
-      </c>
-      <c r="G14" t="str">
         <v>main</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>